--- a/Test2/03_Apriori/V2/Configurations/Scenarios.xlsx
+++ b/Test2/03_Apriori/V2/Configurations/Scenarios.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="88">
   <si>
     <t xml:space="preserve">Scenario_name</t>
   </si>
@@ -54,24 +54,45 @@
     <t xml:space="preserve">OutputPathsIds</t>
   </si>
   <si>
+    <t xml:space="preserve">Adalimumab_Human_0.5_mpk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Global", "Adalimumab_Human"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0, 12, 12;  13, 672, 28 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PKML_Files_Human/PKML_Files_Human/AntiTNFA.pkml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PVB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adalimumab_Human_1_mpk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adalimumab_Human_3_mpk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adalimumab_Human_5_mpk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adalimumab_Human_10_mpk</t>
+  </si>
+  <si>
     <t xml:space="preserve">Adalimumab_Monkey_3_mpk</t>
   </si>
   <si>
     <t xml:space="preserve">"Global", "Adalimumab_Monkey"</t>
   </si>
   <si>
-    <t xml:space="preserve">0, 12, 12;  13, 672, 28 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">h</t>
-  </si>
-  <si>
     <t xml:space="preserve">PKML_Files_Monkey/PKML_Files_Monkey/AntiTNFA.pkml</t>
   </si>
   <si>
-    <t xml:space="preserve">PVB</t>
-  </si>
-  <si>
     <t xml:space="preserve">Atezolizumab_Human_1_mpk</t>
   </si>
   <si>
@@ -154,9 +175,6 @@
   </si>
   <si>
     <t xml:space="preserve">"Global", "Golimumab_Human"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PKML_Files_Human/PKML_Files_Human/AntiTNFA.pkml</t>
   </si>
   <si>
     <t xml:space="preserve">Golimumab_Human_0.3_mpk</t>
@@ -680,7 +698,7 @@
       <c r="C3"/>
       <c r="D3"/>
       <c r="E3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F3" t="s">
         <v>19</v>
@@ -695,7 +713,7 @@
       <c r="J3"/>
       <c r="K3"/>
       <c r="L3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="M3" t="s">
         <v>18</v>
@@ -703,16 +721,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B4"/>
       <c r="C4"/>
       <c r="D4"/>
       <c r="E4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" t="s">
         <v>20</v>
-      </c>
-      <c r="F4" t="s">
-        <v>22</v>
       </c>
       <c r="G4" t="s">
         <v>15</v>
@@ -724,7 +742,7 @@
       <c r="J4"/>
       <c r="K4"/>
       <c r="L4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="M4" t="s">
         <v>18</v>
@@ -732,16 +750,16 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B5"/>
       <c r="C5"/>
       <c r="D5"/>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G5" t="s">
         <v>15</v>
@@ -753,7 +771,7 @@
       <c r="J5"/>
       <c r="K5"/>
       <c r="L5" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="M5" t="s">
         <v>18</v>
@@ -761,16 +779,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B6"/>
       <c r="C6"/>
       <c r="D6"/>
       <c r="E6" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G6" t="s">
         <v>15</v>
@@ -782,7 +800,7 @@
       <c r="J6"/>
       <c r="K6"/>
       <c r="L6" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="M6" t="s">
         <v>18</v>
@@ -790,16 +808,16 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B7"/>
       <c r="C7"/>
       <c r="D7"/>
       <c r="E7" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G7" t="s">
         <v>15</v>
@@ -811,7 +829,7 @@
       <c r="J7"/>
       <c r="K7"/>
       <c r="L7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="M7" t="s">
         <v>18</v>
@@ -912,7 +930,7 @@
       <c r="C11"/>
       <c r="D11"/>
       <c r="E11" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F11" t="s">
         <v>31</v>
@@ -927,7 +945,7 @@
       <c r="J11"/>
       <c r="K11"/>
       <c r="L11" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="M11" t="s">
         <v>18</v>
@@ -935,16 +953,16 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B12"/>
       <c r="C12"/>
       <c r="D12"/>
       <c r="E12" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" t="s">
         <v>32</v>
-      </c>
-      <c r="F12" t="s">
-        <v>33</v>
       </c>
       <c r="G12" t="s">
         <v>15</v>
@@ -956,7 +974,7 @@
       <c r="J12"/>
       <c r="K12"/>
       <c r="L12" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="M12" t="s">
         <v>18</v>
@@ -964,16 +982,16 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B13"/>
       <c r="C13"/>
       <c r="D13"/>
       <c r="E13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G13" t="s">
         <v>15</v>
@@ -985,7 +1003,7 @@
       <c r="J13"/>
       <c r="K13"/>
       <c r="L13" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="M13" t="s">
         <v>18</v>
@@ -993,16 +1011,16 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B14"/>
       <c r="C14"/>
       <c r="D14"/>
       <c r="E14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G14" t="s">
         <v>15</v>
@@ -1014,7 +1032,7 @@
       <c r="J14"/>
       <c r="K14"/>
       <c r="L14" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="M14" t="s">
         <v>18</v>
@@ -1022,16 +1040,16 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B15"/>
       <c r="C15"/>
       <c r="D15"/>
       <c r="E15" t="s">
+        <v>34</v>
+      </c>
+      <c r="F15" t="s">
         <v>37</v>
-      </c>
-      <c r="F15" t="s">
-        <v>36</v>
       </c>
       <c r="G15" t="s">
         <v>15</v>
@@ -1043,7 +1061,7 @@
       <c r="J15"/>
       <c r="K15"/>
       <c r="L15" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="M15" t="s">
         <v>18</v>
@@ -1072,7 +1090,7 @@
       <c r="J16"/>
       <c r="K16"/>
       <c r="L16" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="M16" t="s">
         <v>18</v>
@@ -1080,16 +1098,16 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B17"/>
       <c r="C17"/>
       <c r="D17"/>
       <c r="E17" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G17" t="s">
         <v>15</v>
@@ -1101,7 +1119,7 @@
       <c r="J17"/>
       <c r="K17"/>
       <c r="L17" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="M17" t="s">
         <v>18</v>
@@ -1109,16 +1127,16 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B18"/>
       <c r="C18"/>
       <c r="D18"/>
       <c r="E18" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F18" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G18" t="s">
         <v>15</v>
@@ -1130,7 +1148,7 @@
       <c r="J18"/>
       <c r="K18"/>
       <c r="L18" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="M18" t="s">
         <v>18</v>
@@ -1138,16 +1156,16 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B19"/>
       <c r="C19"/>
       <c r="D19"/>
       <c r="E19" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="F19" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G19" t="s">
         <v>15</v>
@@ -1159,7 +1177,7 @@
       <c r="J19"/>
       <c r="K19"/>
       <c r="L19" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="M19" t="s">
         <v>18</v>
@@ -1167,16 +1185,16 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B20"/>
       <c r="C20"/>
       <c r="D20"/>
       <c r="E20" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F20" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G20" t="s">
         <v>15</v>
@@ -1188,7 +1206,7 @@
       <c r="J20"/>
       <c r="K20"/>
       <c r="L20" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="M20" t="s">
         <v>18</v>
@@ -1196,7 +1214,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B21"/>
       <c r="C21"/>
@@ -1205,7 +1223,7 @@
         <v>46</v>
       </c>
       <c r="F21" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G21" t="s">
         <v>15</v>
@@ -1225,16 +1243,16 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B22"/>
       <c r="C22"/>
       <c r="D22"/>
       <c r="E22" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F22" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G22" t="s">
         <v>15</v>
@@ -1246,7 +1264,7 @@
       <c r="J22"/>
       <c r="K22"/>
       <c r="L22" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="M22" t="s">
         <v>18</v>
@@ -1260,7 +1278,7 @@
       <c r="C23"/>
       <c r="D23"/>
       <c r="E23" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F23" t="s">
         <v>51</v>
@@ -1275,7 +1293,7 @@
       <c r="J23"/>
       <c r="K23"/>
       <c r="L23" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="M23" t="s">
         <v>18</v>
@@ -1289,7 +1307,7 @@
       <c r="C24"/>
       <c r="D24"/>
       <c r="E24" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="F24" t="s">
         <v>52</v>
@@ -1304,7 +1322,7 @@
       <c r="J24"/>
       <c r="K24"/>
       <c r="L24" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="M24" t="s">
         <v>18</v>
@@ -1312,16 +1330,16 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B25"/>
       <c r="C25"/>
       <c r="D25"/>
       <c r="E25" t="s">
+        <v>53</v>
+      </c>
+      <c r="F25" t="s">
         <v>54</v>
-      </c>
-      <c r="F25" t="s">
-        <v>53</v>
       </c>
       <c r="G25" t="s">
         <v>15</v>
@@ -1347,7 +1365,7 @@
       <c r="C26"/>
       <c r="D26"/>
       <c r="E26" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F26" t="s">
         <v>55</v>
@@ -1362,7 +1380,7 @@
       <c r="J26"/>
       <c r="K26"/>
       <c r="L26" t="s">
-        <v>57</v>
+        <v>17</v>
       </c>
       <c r="M26" t="s">
         <v>18</v>
@@ -1370,16 +1388,16 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B27"/>
       <c r="C27"/>
       <c r="D27"/>
       <c r="E27" t="s">
+        <v>53</v>
+      </c>
+      <c r="F27" t="s">
         <v>56</v>
-      </c>
-      <c r="F27" t="s">
-        <v>58</v>
       </c>
       <c r="G27" t="s">
         <v>15</v>
@@ -1391,7 +1409,7 @@
       <c r="J27"/>
       <c r="K27"/>
       <c r="L27" t="s">
-        <v>57</v>
+        <v>17</v>
       </c>
       <c r="M27" t="s">
         <v>18</v>
@@ -1399,16 +1417,16 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B28"/>
       <c r="C28"/>
       <c r="D28"/>
       <c r="E28" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F28" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G28" t="s">
         <v>15</v>
@@ -1420,7 +1438,7 @@
       <c r="J28"/>
       <c r="K28"/>
       <c r="L28" t="s">
-        <v>57</v>
+        <v>17</v>
       </c>
       <c r="M28" t="s">
         <v>18</v>
@@ -1428,16 +1446,16 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B29"/>
       <c r="C29"/>
       <c r="D29"/>
       <c r="E29" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F29" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G29" t="s">
         <v>15</v>
@@ -1449,7 +1467,7 @@
       <c r="J29"/>
       <c r="K29"/>
       <c r="L29" t="s">
-        <v>57</v>
+        <v>17</v>
       </c>
       <c r="M29" t="s">
         <v>18</v>
@@ -1457,16 +1475,16 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B30"/>
       <c r="C30"/>
       <c r="D30"/>
       <c r="E30" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F30" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G30" t="s">
         <v>15</v>
@@ -1478,7 +1496,7 @@
       <c r="J30"/>
       <c r="K30"/>
       <c r="L30" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="M30" t="s">
         <v>18</v>
@@ -1486,16 +1504,16 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B31"/>
       <c r="C31"/>
       <c r="D31"/>
       <c r="E31" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F31" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G31" t="s">
         <v>15</v>
@@ -1507,7 +1525,7 @@
       <c r="J31"/>
       <c r="K31"/>
       <c r="L31" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="M31" t="s">
         <v>18</v>
@@ -1515,16 +1533,16 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B32"/>
       <c r="C32"/>
       <c r="D32"/>
       <c r="E32" t="s">
+        <v>62</v>
+      </c>
+      <c r="F32" t="s">
         <v>64</v>
-      </c>
-      <c r="F32" t="s">
-        <v>63</v>
       </c>
       <c r="G32" t="s">
         <v>15</v>
@@ -1536,7 +1554,7 @@
       <c r="J32"/>
       <c r="K32"/>
       <c r="L32" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="M32" t="s">
         <v>18</v>
@@ -1544,16 +1562,16 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B33"/>
       <c r="C33"/>
       <c r="D33"/>
       <c r="E33" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F33" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G33" t="s">
         <v>15</v>
@@ -1565,7 +1583,7 @@
       <c r="J33"/>
       <c r="K33"/>
       <c r="L33" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="M33" t="s">
         <v>18</v>
@@ -1573,16 +1591,16 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B34"/>
       <c r="C34"/>
       <c r="D34"/>
       <c r="E34" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="F34" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G34" t="s">
         <v>15</v>
@@ -1594,7 +1612,7 @@
       <c r="J34"/>
       <c r="K34"/>
       <c r="L34" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="M34" t="s">
         <v>18</v>
@@ -1602,16 +1620,16 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B35"/>
       <c r="C35"/>
       <c r="D35"/>
       <c r="E35" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="F35" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G35" t="s">
         <v>15</v>
@@ -1623,7 +1641,7 @@
       <c r="J35"/>
       <c r="K35"/>
       <c r="L35" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="M35" t="s">
         <v>18</v>
@@ -1631,16 +1649,16 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B36"/>
       <c r="C36"/>
       <c r="D36"/>
       <c r="E36" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="F36" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="G36" t="s">
         <v>15</v>
@@ -1652,7 +1670,7 @@
       <c r="J36"/>
       <c r="K36"/>
       <c r="L36" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="M36" t="s">
         <v>18</v>
@@ -1660,7 +1678,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B37"/>
       <c r="C37"/>
@@ -1669,7 +1687,7 @@
         <v>70</v>
       </c>
       <c r="F37" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G37" t="s">
         <v>15</v>
@@ -1681,7 +1699,7 @@
       <c r="J37"/>
       <c r="K37"/>
       <c r="L37" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="M37" t="s">
         <v>18</v>
@@ -1689,16 +1707,16 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B38"/>
       <c r="C38"/>
       <c r="D38"/>
       <c r="E38" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="F38" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G38" t="s">
         <v>15</v>
@@ -1710,7 +1728,7 @@
       <c r="J38"/>
       <c r="K38"/>
       <c r="L38" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="M38" t="s">
         <v>18</v>
@@ -1718,16 +1736,16 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B39"/>
       <c r="C39"/>
       <c r="D39"/>
       <c r="E39" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F39" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G39" t="s">
         <v>15</v>
@@ -1739,9 +1757,154 @@
       <c r="J39"/>
       <c r="K39"/>
       <c r="L39" t="s">
+        <v>63</v>
+      </c>
+      <c r="M39" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>75</v>
+      </c>
+      <c r="B40"/>
+      <c r="C40"/>
+      <c r="D40"/>
+      <c r="E40" t="s">
+        <v>76</v>
+      </c>
+      <c r="F40" t="s">
+        <v>75</v>
+      </c>
+      <c r="G40" t="s">
+        <v>15</v>
+      </c>
+      <c r="H40" t="s">
+        <v>16</v>
+      </c>
+      <c r="I40"/>
+      <c r="J40"/>
+      <c r="K40"/>
+      <c r="L40" t="s">
+        <v>71</v>
+      </c>
+      <c r="M40" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>77</v>
+      </c>
+      <c r="B41"/>
+      <c r="C41"/>
+      <c r="D41"/>
+      <c r="E41" t="s">
+        <v>76</v>
+      </c>
+      <c r="F41" t="s">
+        <v>77</v>
+      </c>
+      <c r="G41" t="s">
+        <v>15</v>
+      </c>
+      <c r="H41" t="s">
+        <v>16</v>
+      </c>
+      <c r="I41"/>
+      <c r="J41"/>
+      <c r="K41"/>
+      <c r="L41" t="s">
+        <v>71</v>
+      </c>
+      <c r="M41" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
         <v>78</v>
       </c>
-      <c r="M39" t="s">
+      <c r="B42"/>
+      <c r="C42"/>
+      <c r="D42"/>
+      <c r="E42" t="s">
+        <v>76</v>
+      </c>
+      <c r="F42" t="s">
+        <v>78</v>
+      </c>
+      <c r="G42" t="s">
+        <v>15</v>
+      </c>
+      <c r="H42" t="s">
+        <v>16</v>
+      </c>
+      <c r="I42"/>
+      <c r="J42"/>
+      <c r="K42"/>
+      <c r="L42" t="s">
+        <v>71</v>
+      </c>
+      <c r="M42" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>79</v>
+      </c>
+      <c r="B43"/>
+      <c r="C43"/>
+      <c r="D43"/>
+      <c r="E43" t="s">
+        <v>80</v>
+      </c>
+      <c r="F43" t="s">
+        <v>79</v>
+      </c>
+      <c r="G43" t="s">
+        <v>15</v>
+      </c>
+      <c r="H43" t="s">
+        <v>16</v>
+      </c>
+      <c r="I43"/>
+      <c r="J43"/>
+      <c r="K43"/>
+      <c r="L43" t="s">
+        <v>81</v>
+      </c>
+      <c r="M43" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>82</v>
+      </c>
+      <c r="B44"/>
+      <c r="C44"/>
+      <c r="D44"/>
+      <c r="E44" t="s">
+        <v>83</v>
+      </c>
+      <c r="F44" t="s">
+        <v>82</v>
+      </c>
+      <c r="G44" t="s">
+        <v>15</v>
+      </c>
+      <c r="H44" t="s">
+        <v>16</v>
+      </c>
+      <c r="I44"/>
+      <c r="J44"/>
+      <c r="K44"/>
+      <c r="L44" t="s">
+        <v>84</v>
+      </c>
+      <c r="M44" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1762,10 +1925,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="B1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2">
@@ -1773,7 +1936,7 @@
         <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/Test2/03_Apriori/V2/Configurations/Scenarios.xlsx
+++ b/Test2/03_Apriori/V2/Configurations/Scenarios.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="89">
   <si>
     <t xml:space="preserve">Scenario_name</t>
   </si>
@@ -234,10 +234,13 @@
     <t xml:space="preserve">Nivolumab_Monkey_10_mpk</t>
   </si>
   <si>
-    <t xml:space="preserve">Pembrolizumab_Human_3_mpk</t>
+    <t xml:space="preserve">Pembrolizumab_Human_2_mpk</t>
   </si>
   <si>
     <t xml:space="preserve">"Global", "Pembrolizumab_Human"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pembrolizumab_Human_10_mpk</t>
   </si>
   <si>
     <t xml:space="preserve">Pembrolizumab_Monkey_0.3_mpk</t>
@@ -1771,7 +1774,7 @@
       <c r="C40"/>
       <c r="D40"/>
       <c r="E40" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F40" t="s">
         <v>75</v>
@@ -1786,7 +1789,7 @@
       <c r="J40"/>
       <c r="K40"/>
       <c r="L40" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="M40" t="s">
         <v>18</v>
@@ -1794,16 +1797,16 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B41"/>
       <c r="C41"/>
       <c r="D41"/>
       <c r="E41" t="s">
+        <v>77</v>
+      </c>
+      <c r="F41" t="s">
         <v>76</v>
-      </c>
-      <c r="F41" t="s">
-        <v>77</v>
       </c>
       <c r="G41" t="s">
         <v>15</v>
@@ -1829,7 +1832,7 @@
       <c r="C42"/>
       <c r="D42"/>
       <c r="E42" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F42" t="s">
         <v>78</v>
@@ -1858,7 +1861,7 @@
       <c r="C43"/>
       <c r="D43"/>
       <c r="E43" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F43" t="s">
         <v>79</v>
@@ -1873,7 +1876,7 @@
       <c r="J43"/>
       <c r="K43"/>
       <c r="L43" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="M43" t="s">
         <v>18</v>
@@ -1881,16 +1884,16 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B44"/>
       <c r="C44"/>
       <c r="D44"/>
       <c r="E44" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F44" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G44" t="s">
         <v>15</v>
@@ -1902,9 +1905,38 @@
       <c r="J44"/>
       <c r="K44"/>
       <c r="L44" t="s">
+        <v>82</v>
+      </c>
+      <c r="M44" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>83</v>
+      </c>
+      <c r="B45"/>
+      <c r="C45"/>
+      <c r="D45"/>
+      <c r="E45" t="s">
         <v>84</v>
       </c>
-      <c r="M44" t="s">
+      <c r="F45" t="s">
+        <v>83</v>
+      </c>
+      <c r="G45" t="s">
+        <v>15</v>
+      </c>
+      <c r="H45" t="s">
+        <v>16</v>
+      </c>
+      <c r="I45"/>
+      <c r="J45"/>
+      <c r="K45"/>
+      <c r="L45" t="s">
+        <v>85</v>
+      </c>
+      <c r="M45" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1925,10 +1957,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2">
@@ -1936,7 +1968,7 @@
         <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
